--- a/_doc/AppMsgBox.xlsx
+++ b/_doc/AppMsgBox.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6_YMGLib5\FujisawaIshikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A681B0-3ED9-44AD-AEA5-7B53C3906EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9465B47E-E1D6-4B2C-A958-FF969DE9EEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1140" windowWidth="28800" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6765" yWindow="2085" windowWidth="28395" windowHeight="17145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="109">
   <si>
     <t>Icon</t>
     <phoneticPr fontId="1"/>
@@ -600,6 +600,190 @@
   </si>
   <si>
     <t>{0}を削除しますか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}の引落データを作成します。よろしいですか？</t>
+    <rPh sb="4" eb="6">
+      <t>ヒキオトシ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ConfirmCreateHikiotoshi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>YesNo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Question</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Button2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}の引落データは既に存在します。\r\n作成済みのデータは全てクリアされますが、再作成しますか？</t>
+    <rPh sb="10" eb="11">
+      <t>スデ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="42" eb="45">
+      <t>サイサクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>@c(Red)再作成すると元には戻せません。本当によろしいですか？</t>
+    <rPh sb="7" eb="10">
+      <t>サイサクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ConfirmRemakeHikiotoshi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ConfirmRemakeHikiotoshi2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CancelImportCSV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSVインポートをキャンセルします。よろしいですか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ExecImportCSV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSVファイルからデータのインポートを実行します。よろしいですか？</t>
+    <rPh sb="19" eb="21">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SuccessExportLog</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログファイルの出力が完了しました。</t>
+    <rPh sb="7" eb="9">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CannotDeleteLoginUser</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}は現在ログイン中のため、削除することができません。</t>
+    <rPh sb="4" eb="6">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ConfirmChangePassword</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワードを変更します。よろしいですか？</t>
+    <rPh sb="6" eb="8">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FailedExportLogReasonSave</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログファイルの出力に失敗しました。ファイルがなんらかのアプリケーションによって開かれている可能性があります。</t>
+    <rPh sb="7" eb="9">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="45" eb="48">
+      <t>カノウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CreateHikiotoshiData</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}度の引落データを作成しました。</t>
+    <rPh sb="3" eb="4">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒキオトシ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FailedHikiotoshiData</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何らかの理由で、引落データの作成に失敗しました。</t>
+    <rPh sb="0" eb="1">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒキオトシ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シッパイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1640,92 +1824,224 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="4"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
+      <c r="A31" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="4"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
+      <c r="A32" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="4"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
+      <c r="A33" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="34" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="4"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
+      <c r="A34" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="35" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="4"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
+      <c r="A35" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="36" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="4"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
+      <c r="A36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="37" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="4"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
+      <c r="A37" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="38" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="4"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
+      <c r="A38" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="39" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="4"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
+      <c r="A39" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="40" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="4"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
+      <c r="A40" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="41" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="4"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
+      <c r="A41" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="42" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="4"/>

--- a/_doc/AppMsgBox.xlsx
+++ b/_doc/AppMsgBox.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6_YMGLib5\FujisawaIshikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9465B47E-E1D6-4B2C-A958-FF969DE9EEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B844FA-749F-45EA-A0CA-1C0FA3E362CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6765" yWindow="2085" windowWidth="28395" windowHeight="17145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10875" yWindow="3900" windowWidth="43200" windowHeight="17145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="113">
   <si>
     <t>Icon</t>
     <phoneticPr fontId="1"/>
@@ -783,6 +783,43 @@
     </rPh>
     <rPh sb="17" eb="19">
       <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ConfirmRemakeHikiotoshiOnlyOne</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}の引落データを再作成します。\r\n作成済みのデータは全てクリアされますが、よろしいですか？</t>
+    <rPh sb="10" eb="13">
+      <t>サイサクセイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>スベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RemakeHikiotoshiData</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}の引落データを再作成しました。</t>
+    <rPh sb="4" eb="6">
+      <t>ヒキオトシ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サクセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2044,20 +2081,44 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="4"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
+      <c r="A42" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="43" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="4"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
+      <c r="A43" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="44" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4"/>
